--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11537-Table_part.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11537-Table_part.xlsx
@@ -943,7 +943,7 @@
     <t>Increment multiplier</t>
   </si>
   <si>
-    <t>i++</t>
+    <t>i += 1</t>
   </si>
   <si>
     <t>TablePart Table19 row 1 of 2</t>
